--- a/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="285">
   <si>
     <t>Component list</t>
   </si>
@@ -862,6 +862,18 @@
   </si>
   <si>
     <t>R3, R11</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>LC-2030C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shengwei </t>
+  </si>
+  <si>
+    <t>C3011736</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1895,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2208,7 +2220,7 @@
     <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B51" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -4270,7 +4282,9 @@
       <c r="H48" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="I48" s="37"/>
+      <c r="I48" s="37" t="s">
+        <v>254</v>
+      </c>
       <c r="J48" s="37" t="s">
         <v>208</v>
       </c>
@@ -4324,7 +4338,9 @@
       <c r="H49" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="I49" s="51"/>
+      <c r="I49" s="51" t="s">
+        <v>254</v>
+      </c>
       <c r="J49" s="51" t="s">
         <v>209</v>
       </c>
@@ -4378,7 +4394,9 @@
       <c r="H50" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="I50" s="37"/>
+      <c r="I50" s="37" t="s">
+        <v>254</v>
+      </c>
       <c r="J50" s="37" t="s">
         <v>210</v>
       </c>
@@ -4432,7 +4450,9 @@
       <c r="H51" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="I51" s="51"/>
+      <c r="I51" s="51" t="s">
+        <v>254</v>
+      </c>
       <c r="J51" s="51" t="s">
         <v>211</v>
       </c>
@@ -4443,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="51">
-        <f t="shared" ref="M51" si="41">L51*5</f>
+        <f t="shared" ref="M51:M52" si="41">L51*5</f>
         <v>5</v>
       </c>
       <c r="N51" s="51">
@@ -4456,71 +4476,127 @@
         <v>0.25240000000000001</v>
       </c>
       <c r="Q51" s="52">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
+        <f t="shared" ref="Q51:Q52" si="42">P51*N51</f>
         <v>1.5144000000000002</v>
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
     </row>
-    <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="45"/>
-      <c r="M52" s="45"/>
-      <c r="N52" s="73" t="s">
+      <c r="B52" s="47">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="G52" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="H52" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="I52" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="J52" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="K52" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="L52" s="51">
+        <v>1</v>
+      </c>
+      <c r="M52" s="51">
+        <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O52" s="74"/>
-      <c r="P52" s="74"/>
-      <c r="Q52" s="48">
-        <f>SUM(Q10:Q51)</f>
-        <v>90.486700000000013</v>
-      </c>
-      <c r="R52" s="69"/>
-      <c r="S52" s="70"/>
+      <c r="N52" s="51">
+        <v>5</v>
+      </c>
+      <c r="O52" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="P52" s="52">
+        <v>1.3189</v>
+      </c>
+      <c r="Q52" s="52">
+        <f t="shared" si="42"/>
+        <v>6.5945</v>
+      </c>
+      <c r="R52" s="51"/>
+      <c r="S52" s="39"/>
     </row>
     <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
       <c r="N53" s="73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O53" s="74"/>
       <c r="P53" s="74"/>
-      <c r="Q53" s="49">
-        <f>Q52/5</f>
-        <v>18.097340000000003</v>
-      </c>
-      <c r="R53" s="71"/>
-      <c r="S53" s="72"/>
+      <c r="Q53" s="48">
+        <f>SUM(Q10:Q52)</f>
+        <v>97.08120000000001</v>
+      </c>
+      <c r="R53" s="69"/>
+      <c r="S53" s="70"/>
+    </row>
+    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="O54" s="74"/>
+      <c r="P54" s="74"/>
+      <c r="Q54" s="49">
+        <f>Q53/5</f>
+        <v>19.416240000000002</v>
+      </c>
+      <c r="R54" s="71"/>
+      <c r="S54" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R52:S53"/>
-    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N54:P54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -4564,9 +4640,10 @@
     <hyperlink ref="O25" r:id="rId39"/>
     <hyperlink ref="O47" r:id="rId40"/>
     <hyperlink ref="O22" r:id="rId41"/>
+    <hyperlink ref="O52" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
-  <drawing r:id="rId43"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
--- a/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="284">
   <si>
     <t>Component list</t>
   </si>
@@ -195,9 +195,6 @@
     <t>U3</t>
   </si>
   <si>
-    <t>U4</t>
-  </si>
-  <si>
     <t>X1</t>
   </si>
   <si>
@@ -315,9 +312,6 @@
     <t>SPI LQFP-48(7x7) Ethernet ICs ROHS</t>
   </si>
   <si>
-    <t>TVS DIODE 5.5VWM 8.5VC SOT23-5</t>
-  </si>
-  <si>
     <t>SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
@@ -375,9 +369,6 @@
     <t>48-LQFP (7x7)_</t>
   </si>
   <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
     <t>NX3225GA-25MHZ-STD-CRG-2</t>
   </si>
   <si>
@@ -489,9 +480,6 @@
     <t>W5500</t>
   </si>
   <si>
-    <t>SP0504BAHTG</t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -651,9 +639,6 @@
     <t>C32843</t>
   </si>
   <si>
-    <t>C10675</t>
-  </si>
-  <si>
     <t>C438901</t>
   </si>
   <si>
@@ -874,6 +859,18 @@
   </si>
   <si>
     <t>C3011736</t>
+  </si>
+  <si>
+    <t>D3, D4</t>
+  </si>
+  <si>
+    <t>TVS DIODE 5.5VWM 8.5VC SOT23-3</t>
+  </si>
+  <si>
+    <t>SP0502BAHTG</t>
+  </si>
+  <si>
+    <t>C207261</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1947,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1975,7 +1972,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2000,7 +1997,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2116,49 +2113,49 @@
         <v>20</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>241</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="P9" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="K9" s="60" t="s">
+      <c r="Q9" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>248</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2174,25 +2171,25 @@
         <v>21</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L10" s="37">
         <v>10</v>
@@ -2205,7 +2202,7 @@
         <v>100</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P10" s="38">
         <v>1.0500000000000001E-2</v>
@@ -2230,23 +2227,23 @@
         <v>22</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I11" s="51"/>
       <c r="J11" s="51" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2259,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P11" s="52">
         <v>1.7399999999999999E-2</v>
@@ -2284,25 +2281,25 @@
         <v>23</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L12" s="37">
         <v>3</v>
@@ -2315,7 +2312,7 @@
         <v>50</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P12" s="38">
         <v>1.06E-2</v>
@@ -2340,23 +2337,23 @@
         <v>24</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I13" s="51"/>
       <c r="J13" s="51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2369,7 +2366,7 @@
         <v>6</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P13" s="52">
         <v>1.1597999999999999</v>
@@ -2394,23 +2391,23 @@
         <v>25</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2423,7 +2420,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P14" s="38">
         <v>2.5000000000000001E-3</v>
@@ -2448,25 +2445,25 @@
         <v>26</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L15" s="51">
         <v>3</v>
@@ -2479,7 +2476,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P15" s="52">
         <v>1.9E-3</v>
@@ -2504,23 +2501,23 @@
         <v>27</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2533,7 +2530,7 @@
         <v>6</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P16" s="38">
         <v>0.84960000000000002</v>
@@ -2558,23 +2555,23 @@
         <v>28</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="51" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2587,7 +2584,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P17" s="52">
         <v>2.8E-3</v>
@@ -2612,23 +2609,23 @@
         <v>29</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2641,7 +2638,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P18" s="38">
         <v>6.8999999999999999E-3</v>
@@ -2666,23 +2663,23 @@
         <v>30</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I19" s="51"/>
       <c r="J19" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -2695,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P19" s="52">
         <v>4.2299999999999997E-2</v>
@@ -2720,23 +2717,23 @@
         <v>31</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I20" s="37"/>
       <c r="J20" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2749,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P20" s="38">
         <v>4.6899999999999997E-2</v>
@@ -2774,36 +2771,36 @@
         <v>32</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I21" s="51"/>
       <c r="J21" s="51" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
       </c>
       <c r="M21" s="51">
-        <f t="shared" ref="M21" si="11">L21*5</f>
+        <f t="shared" ref="M21:M22" si="11">L21*5</f>
         <v>5</v>
       </c>
       <c r="N21" s="51">
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P21" s="52">
         <v>4.5600000000000002E-2</v>
@@ -2815,1111 +2812,1098 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="46">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="47">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>33</v>
+        <v>280</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="K22" s="37" t="s">
-        <v>254</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="K22" s="37"/>
       <c r="L22" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="37">
-        <f>L22*5</f>
-        <v>5</v>
-      </c>
-      <c r="N22" s="37">
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="O22" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P22" s="38">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="Q22" s="38">
-        <f>P22*N22</f>
-        <v>0.92999999999999994</v>
-      </c>
+      <c r="N22" s="37"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="47">
-        <f t="shared" si="0"/>
+      <c r="B23" s="46">
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="L23" s="51">
-        <v>2</v>
-      </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="13">L23*5</f>
+      <c r="C23" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f>L23*5</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="37">
         <v>10</v>
       </c>
-      <c r="N23" s="51">
-        <v>15</v>
-      </c>
       <c r="O23" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P23" s="52">
-        <v>0.18790000000000001</v>
-      </c>
-      <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>2.8185000000000002</v>
-      </c>
-      <c r="R23" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P23" s="38">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="47">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="53" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>257</v>
-      </c>
-      <c r="G24" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="H24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="I24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="J24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="K24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="L24" s="62">
-        <v>1</v>
-      </c>
-      <c r="M24" s="62">
-        <f>L24*5</f>
-        <v>5</v>
-      </c>
-      <c r="N24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="O24" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="P24" s="64" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q24" s="64" t="s">
-        <v>254</v>
-      </c>
-      <c r="R24" s="37"/>
+      <c r="C24" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L24" s="51">
+        <v>2</v>
+      </c>
+      <c r="M24" s="51">
+        <f t="shared" ref="M24" si="13">L24*5</f>
+        <v>10</v>
+      </c>
+      <c r="N24" s="51">
+        <v>15</v>
+      </c>
+      <c r="O24" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P24" s="52">
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="Q24" s="52">
+        <f t="shared" ref="Q24" si="14">P24*N24</f>
+        <v>2.8185000000000002</v>
+      </c>
+      <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="47">
+      <c r="B25" s="46">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="I25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="J25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="K25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="L25" s="62">
+        <v>1</v>
+      </c>
+      <c r="M25" s="62">
+        <f>L25*5</f>
+        <v>5</v>
+      </c>
+      <c r="N25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="O25" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="P25" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q25" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="R25" s="37"/>
+      <c r="S25" s="59"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="47">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D26" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J25" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="K25" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="L25" s="51">
+      <c r="E26" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L26" s="51">
         <v>1</v>
       </c>
-      <c r="M25" s="51">
-        <f t="shared" ref="M25" si="15">L25*5</f>
+      <c r="M26" s="51">
+        <f t="shared" ref="M26" si="15">L26*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="51">
+      <c r="N26" s="51">
         <v>6</v>
       </c>
-      <c r="O25" s="61" t="s">
-        <v>269</v>
-      </c>
-      <c r="P25" s="52">
+      <c r="O26" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="P26" s="52">
         <v>3.47</v>
       </c>
-      <c r="Q25" s="52">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
+      <c r="Q26" s="52">
+        <f t="shared" ref="Q26" si="16">P26*N26</f>
         <v>20.82</v>
       </c>
-      <c r="R25" s="51"/>
-      <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
-        <v>17</v>
-      </c>
-      <c r="C26" s="53" t="s">
+      <c r="R26" s="51"/>
+      <c r="S26" s="59"/>
+    </row>
+    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="46">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D27" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="L26" s="37">
+      <c r="E27" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="L27" s="37">
         <v>1</v>
       </c>
-      <c r="M26" s="37">
-        <f>L26*5</f>
+      <c r="M27" s="37">
+        <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N26" s="37">
+      <c r="N27" s="37">
         <v>6</v>
       </c>
-      <c r="O26" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P26" s="38">
+      <c r="O27" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P27" s="38">
         <v>0.94820000000000004</v>
       </c>
-      <c r="Q26" s="38">
-        <f>P26*N26</f>
+      <c r="Q27" s="38">
+        <f>P27*N27</f>
         <v>5.6892000000000005</v>
       </c>
-      <c r="R26" s="37"/>
-      <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="47">
+      <c r="R27" s="37"/>
+      <c r="S27" s="59"/>
+    </row>
+    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="47">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="H27" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="L27" s="51">
-        <v>1</v>
-      </c>
-      <c r="M27" s="51">
-        <f t="shared" ref="M27" si="17">L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="51">
-        <v>20</v>
-      </c>
-      <c r="O27" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P27" s="52">
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0.67</v>
-      </c>
-      <c r="R27" s="51"/>
-      <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="L28" s="51">
+        <v>1</v>
+      </c>
+      <c r="M28" s="51">
+        <f t="shared" ref="M28" si="17">L28*5</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="51">
+        <v>20</v>
+      </c>
+      <c r="O28" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P28" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q28" s="52">
+        <f t="shared" ref="Q28" si="18">P28*N28</f>
+        <v>0.67</v>
+      </c>
+      <c r="R28" s="51"/>
+      <c r="S28" s="59"/>
+    </row>
+    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="46">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="37" t="s">
+      <c r="E29" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="K29" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f>L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="37">
+        <v>6</v>
+      </c>
+      <c r="O29" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P29" s="38">
+        <v>0.3453</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>2.0718000000000001</v>
+      </c>
+      <c r="R29" s="37"/>
+      <c r="S29" s="59"/>
+    </row>
+    <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="47">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="K28" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="L28" s="37">
+      <c r="F30" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="H30" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="K30" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="L30" s="51">
         <v>1</v>
       </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
+      <c r="M30" s="51">
+        <f t="shared" ref="M30" si="19">L30*5</f>
         <v>5</v>
       </c>
-      <c r="N28" s="37">
-        <v>6</v>
-      </c>
-      <c r="O28" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P28" s="38">
-        <v>0.3453</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>2.0718000000000001</v>
-      </c>
-      <c r="R28" s="37"/>
-      <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="47">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="H29" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="K29" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="L29" s="51">
-        <v>1</v>
-      </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="19">L29*5</f>
-        <v>5</v>
-      </c>
-      <c r="N29" s="51">
+      <c r="N30" s="51">
         <v>100</v>
       </c>
-      <c r="O29" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P29" s="52">
+      <c r="O30" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P30" s="52">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
+      <c r="Q30" s="52">
+        <f t="shared" ref="Q30" si="20">P30*N30</f>
         <v>0.06</v>
       </c>
-      <c r="R29" s="51"/>
-      <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
-        <v>21</v>
-      </c>
-      <c r="C30" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="L30" s="37">
-        <v>1</v>
-      </c>
-      <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
-      </c>
-      <c r="N30" s="37">
-        <v>50</v>
-      </c>
-      <c r="O30" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P30" s="38">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="Q30" s="38">
-        <f>P30*N30</f>
-        <v>0.27499999999999997</v>
-      </c>
-      <c r="R30" s="37"/>
+      <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
-        <f t="shared" si="0"/>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J31" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="K31" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="L31" s="51">
-        <v>2</v>
-      </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="21">L31*5</f>
-        <v>10</v>
-      </c>
-      <c r="N31" s="51">
-        <v>100</v>
+      <c r="D31" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="L31" s="37">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f>L31*5</f>
+        <v>5</v>
+      </c>
+      <c r="N31" s="37">
+        <v>50</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P31" s="52">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R31" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P31" s="38">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>0.27499999999999997</v>
+      </c>
+      <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="47">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="L32" s="37">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37">
+      <c r="D32" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="H32" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J32" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="L32" s="51">
+        <v>2</v>
+      </c>
+      <c r="M32" s="51">
+        <f t="shared" ref="M32" si="21">L32*5</f>
         <v>10</v>
       </c>
+      <c r="N32" s="51">
+        <v>100</v>
+      </c>
       <c r="O32" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P32" s="38">
-        <v>7.4800000000000005E-2</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>0.748</v>
-      </c>
-      <c r="R32" s="37"/>
+        <v>251</v>
+      </c>
+      <c r="P32" s="52">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q32" s="52">
+        <f t="shared" ref="Q32" si="22">P32*N32</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
+        <v>10</v>
+      </c>
+      <c r="O33" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P33" s="38">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>0.748</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="59"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="47">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="D34" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="H33" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I33" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J33" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="K33" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="L33" s="51">
+      <c r="E34" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="H34" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I34" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J34" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="K34" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="L34" s="51">
         <v>1</v>
       </c>
-      <c r="M33" s="51">
-        <f t="shared" ref="M33" si="23">L33*5</f>
+      <c r="M34" s="51">
+        <f t="shared" ref="M34" si="23">L34*5</f>
         <v>5</v>
       </c>
-      <c r="N33" s="51">
+      <c r="N34" s="51">
         <v>100</v>
       </c>
-      <c r="O33" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P33" s="52">
+      <c r="O34" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P34" s="52">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
+      <c r="Q34" s="52">
+        <f t="shared" ref="Q34" si="24">P34*N34</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R33" s="51"/>
-      <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="L34" s="37">
-        <v>1</v>
-      </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="37">
-        <v>100</v>
-      </c>
-      <c r="O34" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P34" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
-        <v>0.1</v>
-      </c>
-      <c r="R34" s="37"/>
+      <c r="R34" s="51"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="47">
-        <f t="shared" si="0"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G35" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="J35" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="K35" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="L35" s="51">
+      <c r="D35" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="L35" s="37">
         <v>1</v>
       </c>
-      <c r="M35" s="51">
-        <f t="shared" ref="M35" si="25">L35*5</f>
+      <c r="M35" s="37">
+        <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="51">
+      <c r="N35" s="37">
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P35" s="52">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
-        <v>0.12</v>
-      </c>
-      <c r="R35" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P35" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>0.1</v>
+      </c>
+      <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="46">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="47">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="37">
+      <c r="D36" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I36" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="J36" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="K36" s="51" t="s">
+        <v>224</v>
+      </c>
+      <c r="L36" s="51">
         <v>1</v>
       </c>
-      <c r="M36" s="37">
-        <f>L36*5</f>
+      <c r="M36" s="51">
+        <f t="shared" ref="M36" si="25">L36*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="51">
         <v>100</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P36" s="38">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>0.09</v>
-      </c>
-      <c r="R36" s="37"/>
+        <v>251</v>
+      </c>
+      <c r="P36" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q36" s="52">
+        <f t="shared" ref="Q36" si="26">P36*N36</f>
+        <v>0.12</v>
+      </c>
+      <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="47">
+      <c r="B37" s="46">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="L37" s="37">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f>L37*5</f>
+        <v>5</v>
+      </c>
+      <c r="N37" s="37">
+        <v>100</v>
+      </c>
+      <c r="O37" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P37" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>0.09</v>
+      </c>
+      <c r="R37" s="37"/>
+      <c r="S37" s="59"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="47">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="51" t="s">
+      <c r="D38" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J37" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="K37" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="L37" s="51">
+      <c r="E38" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="H38" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J38" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="K38" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="L38" s="51">
         <v>1</v>
       </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="27">L37*5</f>
+      <c r="M38" s="51">
+        <f t="shared" ref="M38" si="27">L38*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="51">
+      <c r="N38" s="51">
         <v>50</v>
       </c>
-      <c r="O37" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P37" s="52">
+      <c r="O38" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P38" s="52">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
+      <c r="Q38" s="52">
+        <f t="shared" ref="Q38" si="28">P38*N38</f>
         <v>0.27499999999999997</v>
       </c>
-      <c r="R37" s="51"/>
-      <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="46">
-        <f>ROW(B38) - ROW($B$9)</f>
-        <v>29</v>
-      </c>
-      <c r="C38" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="L38" s="37">
-        <v>13</v>
-      </c>
-      <c r="M38" s="37">
-        <f>L38*5</f>
-        <v>65</v>
-      </c>
-      <c r="N38" s="37">
-        <v>100</v>
-      </c>
-      <c r="O38" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P38" s="38">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>0.09</v>
-      </c>
-      <c r="R38" s="37"/>
+      <c r="R38" s="51"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="47">
+      <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="H39" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I39" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J39" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="K39" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="L39" s="51">
-        <v>3</v>
-      </c>
-      <c r="M39" s="51">
-        <f t="shared" ref="M39" si="29">L39*5</f>
-        <v>15</v>
-      </c>
-      <c r="N39" s="51">
+      <c r="D39" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="L39" s="37">
+        <v>13</v>
+      </c>
+      <c r="M39" s="37">
+        <f>L39*5</f>
+        <v>65</v>
+      </c>
+      <c r="N39" s="37">
         <v>100</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P39" s="52">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q39" s="52">
-        <f t="shared" ref="Q39" si="30">P39*N39</f>
-        <v>0.13</v>
-      </c>
-      <c r="R39" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P39" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>0.09</v>
+      </c>
+      <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="47">
-        <f t="shared" si="0"/>
+        <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="54" t="s">
         <v>16</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>48</v>
+        <v>270</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H40" s="51" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I40" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J40" s="51" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L40" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" s="51">
-        <f t="shared" ref="M40" si="31">L40*5</f>
-        <v>5</v>
+        <f t="shared" ref="M40" si="29">L40*5</f>
+        <v>15</v>
       </c>
       <c r="N40" s="51">
         <v>100</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P40" s="52">
-        <v>1E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q40" s="52">
-        <f t="shared" ref="Q40" si="32">P40*N40</f>
-        <v>0.1</v>
+        <f t="shared" ref="Q40" si="30">P40*N40</f>
+        <v>0.13</v>
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="46">
-        <f>ROW(B41) - ROW($B$9)</f>
+      <c r="B41" s="47">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="L41" s="37">
-        <v>2</v>
-      </c>
-      <c r="M41" s="37">
-        <f>L41*5</f>
-        <v>10</v>
-      </c>
-      <c r="N41" s="37">
+      <c r="D41" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I41" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J41" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="K41" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="L41" s="51">
+        <v>1</v>
+      </c>
+      <c r="M41" s="51">
+        <f t="shared" ref="M41" si="31">L41*5</f>
+        <v>5</v>
+      </c>
+      <c r="N41" s="51">
         <v>100</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P41" s="38">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q41" s="38">
-        <f>P41*N41</f>
-        <v>0.11</v>
-      </c>
-      <c r="R41" s="37"/>
+        <v>251</v>
+      </c>
+      <c r="P41" s="52">
+        <v>1E-3</v>
+      </c>
+      <c r="Q41" s="52">
+        <f t="shared" ref="Q41" si="32">P41*N41</f>
+        <v>0.1</v>
+      </c>
+      <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -3932,498 +3916,498 @@
         <v>16</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L42" s="37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" s="37">
         <f>L42*5</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N42" s="37">
         <v>100</v>
       </c>
       <c r="O42" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P42" s="38">
-        <v>1E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="47">
-        <f t="shared" si="0"/>
+      <c r="B43" s="46">
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C43" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D43" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="H43" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I43" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J43" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="K43" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="L43" s="51">
-        <v>1</v>
-      </c>
-      <c r="M43" s="51">
-        <f t="shared" ref="M43" si="33">L43*5</f>
-        <v>5</v>
-      </c>
-      <c r="N43" s="51">
+      <c r="D43" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J43" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="K43" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="L43" s="37">
+        <v>4</v>
+      </c>
+      <c r="M43" s="37">
+        <f>L43*5</f>
+        <v>20</v>
+      </c>
+      <c r="N43" s="37">
         <v>100</v>
       </c>
       <c r="O43" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P43" s="52">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="Q43" s="52">
-        <f t="shared" ref="Q43" si="34">P43*N43</f>
-        <v>0.27</v>
-      </c>
-      <c r="R43" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P43" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q43" s="38">
+        <f>P43*N43</f>
+        <v>0.1</v>
+      </c>
+      <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="46">
-        <f>ROW(B44) - ROW($B$9)</f>
+      <c r="B44" s="47">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="53" t="s">
+      <c r="C44" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D44" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J44" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="K44" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="L44" s="37">
-        <v>4</v>
-      </c>
-      <c r="M44" s="37">
-        <f>L44*5</f>
-        <v>20</v>
-      </c>
-      <c r="N44" s="37">
+      <c r="D44" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I44" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J44" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="K44" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="L44" s="51">
+        <v>1</v>
+      </c>
+      <c r="M44" s="51">
+        <f t="shared" ref="M44" si="33">L44*5</f>
+        <v>5</v>
+      </c>
+      <c r="N44" s="51">
         <v>100</v>
       </c>
       <c r="O44" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P44" s="38">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q44" s="38">
-        <f>P44*N44</f>
-        <v>0.12</v>
-      </c>
-      <c r="R44" s="37"/>
+        <v>251</v>
+      </c>
+      <c r="P44" s="52">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q44" s="52">
+        <f t="shared" ref="Q44" si="34">P44*N44</f>
+        <v>0.27</v>
+      </c>
+      <c r="R44" s="51"/>
       <c r="S44" s="59"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="47">
-        <f t="shared" si="0"/>
+      <c r="B45" s="46">
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="H45" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I45" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J45" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="K45" s="51" t="s">
-        <v>239</v>
-      </c>
-      <c r="L45" s="51">
-        <v>1</v>
-      </c>
-      <c r="M45" s="51">
-        <f t="shared" ref="M45" si="35">L45*5</f>
-        <v>5</v>
-      </c>
-      <c r="N45" s="51">
+      <c r="D45" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J45" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="K45" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="L45" s="37">
+        <v>4</v>
+      </c>
+      <c r="M45" s="37">
+        <f>L45*5</f>
+        <v>20</v>
+      </c>
+      <c r="N45" s="37">
         <v>100</v>
       </c>
       <c r="O45" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P45" s="52">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q45" s="52">
-        <f t="shared" ref="Q45" si="36">P45*N45</f>
-        <v>0.13</v>
-      </c>
-      <c r="R45" s="51"/>
+        <v>251</v>
+      </c>
+      <c r="P45" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q45" s="38">
+        <f>P45*N45</f>
+        <v>0.12</v>
+      </c>
+      <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="46">
-        <f>ROW(B46) - ROW($B$9)</f>
+      <c r="B46" s="47">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="G46" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J46" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="K46" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="L46" s="37">
+      <c r="D46" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="G46" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="H46" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J46" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="K46" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="L46" s="51">
         <v>1</v>
       </c>
-      <c r="M46" s="37">
-        <f>L46*5</f>
+      <c r="M46" s="51">
+        <f t="shared" ref="M46" si="35">L46*5</f>
         <v>5</v>
       </c>
-      <c r="N46" s="37">
+      <c r="N46" s="51">
         <v>100</v>
       </c>
       <c r="O46" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P46" s="38">
+        <v>251</v>
+      </c>
+      <c r="P46" s="52">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q46" s="38">
-        <f>P46*N46</f>
+      <c r="Q46" s="52">
+        <f t="shared" ref="Q46" si="36">P46*N46</f>
         <v>0.13</v>
       </c>
-      <c r="R46" s="37"/>
+      <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="47">
+      <c r="B47" s="46">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G47" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="H47" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="K47" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="L47" s="37">
+        <v>1</v>
+      </c>
+      <c r="M47" s="37">
+        <f>L47*5</f>
+        <v>5</v>
+      </c>
+      <c r="N47" s="37">
+        <v>100</v>
+      </c>
+      <c r="O47" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P47" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q47" s="38">
+        <f>P47*N47</f>
+        <v>0.13</v>
+      </c>
+      <c r="R47" s="37"/>
+      <c r="S47" s="59"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="47">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="51" t="s">
+      <c r="D48" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F47" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>272</v>
-      </c>
-      <c r="H47" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J47" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="K47" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="L47" s="51">
+      <c r="E48" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F48" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="H48" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="I48" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J48" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="K48" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L48" s="51">
         <v>1</v>
       </c>
-      <c r="M47" s="51">
-        <f t="shared" ref="M47" si="37">L47*5</f>
+      <c r="M48" s="51">
+        <f t="shared" ref="M48" si="37">L48*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="51">
+      <c r="N48" s="51">
         <v>6</v>
       </c>
-      <c r="O47" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P47" s="52">
+      <c r="O48" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P48" s="52">
         <v>2.1716000000000002</v>
       </c>
-      <c r="Q47" s="52">
-        <f t="shared" ref="Q47" si="38">P47*N47</f>
+      <c r="Q48" s="52">
+        <f t="shared" ref="Q48" si="38">P48*N48</f>
         <v>13.029600000000002</v>
       </c>
-      <c r="R47" s="51"/>
-      <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="46">
-        <f>ROW(B48) - ROW($B$9)</f>
-        <v>39</v>
-      </c>
-      <c r="C48" s="53" t="s">
+      <c r="R48" s="51"/>
+      <c r="S48" s="59"/>
+    </row>
+    <row r="49" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="46">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D49" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J48" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="K48" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="L48" s="37">
+      <c r="E49" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="L49" s="37">
         <v>1</v>
       </c>
-      <c r="M48" s="37">
-        <f>L48*5</f>
+      <c r="M49" s="37">
+        <f>L49*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="37">
+      <c r="N49" s="37">
         <v>6</v>
       </c>
-      <c r="O48" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P48" s="38">
+      <c r="O49" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="P49" s="38">
         <v>0.64910000000000001</v>
       </c>
-      <c r="Q48" s="38">
-        <f>P48*N48</f>
+      <c r="Q49" s="38">
+        <f>P49*N49</f>
         <v>3.8946000000000001</v>
       </c>
-      <c r="R48" s="37"/>
-      <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="47">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="F49" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="G49" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="H49" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="I49" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="J49" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="K49" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="L49" s="51">
-        <v>1</v>
-      </c>
-      <c r="M49" s="51">
-        <f t="shared" ref="M49" si="39">L49*5</f>
-        <v>5</v>
-      </c>
-      <c r="N49" s="51">
-        <v>6</v>
-      </c>
-      <c r="O49" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P49" s="52">
-        <v>2.6839</v>
-      </c>
-      <c r="Q49" s="52">
-        <f t="shared" ref="Q49" si="40">P49*N49</f>
-        <v>16.103400000000001</v>
-      </c>
-      <c r="R49" s="51"/>
+      <c r="R49" s="37"/>
       <c r="S49" s="59"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="46">
-        <f>ROW(B50) - ROW($B$9)</f>
+      <c r="B50" s="47">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J50" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K50" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="L50" s="37">
+      <c r="C50" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="I50" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J50" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="K50" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="51">
         <v>1</v>
       </c>
-      <c r="M50" s="37">
-        <f>L50*5</f>
+      <c r="M50" s="51">
+        <f t="shared" ref="M50" si="39">L50*5</f>
         <v>5</v>
       </c>
-      <c r="N50" s="37">
+      <c r="N50" s="51">
         <v>6</v>
       </c>
       <c r="O50" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="P50" s="38">
-        <v>0.56479999999999997</v>
-      </c>
-      <c r="Q50" s="38">
-        <f>P50*N50</f>
-        <v>3.3887999999999998</v>
-      </c>
-      <c r="R50" s="37"/>
+        <v>251</v>
+      </c>
+      <c r="P50" s="52">
+        <v>2.6839</v>
+      </c>
+      <c r="Q50" s="52">
+        <f t="shared" ref="Q50" si="40">P50*N50</f>
+        <v>16.103400000000001</v>
+      </c>
+      <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
     <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4436,28 +4420,28 @@
         <v>19</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I51" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J51" s="51" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -4470,7 +4454,7 @@
         <v>6</v>
       </c>
       <c r="O51" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P51" s="52">
         <v>0.25240000000000001</v>
@@ -4489,31 +4473,31 @@
         <v>43</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D52" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F52" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G52" s="51" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J52" s="51" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L52" s="51">
         <v>1</v>
@@ -4526,7 +4510,7 @@
         <v>5</v>
       </c>
       <c r="O52" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P52" s="52">
         <v>1.3189</v>
@@ -4559,7 +4543,7 @@
       <c r="P53" s="74"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
-        <v>97.08120000000001</v>
+        <v>93.692400000000006</v>
       </c>
       <c r="R53" s="69"/>
       <c r="S53" s="70"/>
@@ -4585,7 +4569,7 @@
       <c r="P54" s="74"/>
       <c r="Q54" s="49">
         <f>Q53/5</f>
-        <v>19.416240000000002</v>
+        <v>18.738480000000003</v>
       </c>
       <c r="R54" s="71"/>
       <c r="S54" s="72"/>
@@ -4609,41 +4593,40 @@
     <hyperlink ref="O19" r:id="rId8"/>
     <hyperlink ref="O20" r:id="rId9"/>
     <hyperlink ref="O21" r:id="rId10"/>
-    <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O26" r:id="rId12"/>
-    <hyperlink ref="O27" r:id="rId13"/>
-    <hyperlink ref="O28" r:id="rId14"/>
-    <hyperlink ref="O29" r:id="rId15"/>
-    <hyperlink ref="O30" r:id="rId16"/>
-    <hyperlink ref="O31" r:id="rId17"/>
-    <hyperlink ref="O32" r:id="rId18"/>
-    <hyperlink ref="O33" r:id="rId19"/>
-    <hyperlink ref="O34" r:id="rId20"/>
-    <hyperlink ref="O36" r:id="rId21"/>
-    <hyperlink ref="O37" r:id="rId22"/>
-    <hyperlink ref="O38" r:id="rId23"/>
-    <hyperlink ref="O40" r:id="rId24"/>
-    <hyperlink ref="O41" r:id="rId25"/>
-    <hyperlink ref="O39" r:id="rId26"/>
-    <hyperlink ref="O42" r:id="rId27"/>
-    <hyperlink ref="O43" r:id="rId28"/>
-    <hyperlink ref="O44" r:id="rId29"/>
-    <hyperlink ref="O45" r:id="rId30"/>
-    <hyperlink ref="O46" r:id="rId31"/>
-    <hyperlink ref="O48" r:id="rId32"/>
-    <hyperlink ref="O49" r:id="rId33"/>
-    <hyperlink ref="O50" r:id="rId34"/>
-    <hyperlink ref="O51" r:id="rId35"/>
-    <hyperlink ref="O12" r:id="rId36"/>
-    <hyperlink ref="O15" r:id="rId37"/>
-    <hyperlink ref="O35" r:id="rId38"/>
-    <hyperlink ref="O25" r:id="rId39"/>
-    <hyperlink ref="O47" r:id="rId40"/>
-    <hyperlink ref="O22" r:id="rId41"/>
-    <hyperlink ref="O52" r:id="rId42"/>
+    <hyperlink ref="O24" r:id="rId11"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O28" r:id="rId13"/>
+    <hyperlink ref="O29" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O31" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O35" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O39" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O42" r:id="rId25"/>
+    <hyperlink ref="O40" r:id="rId26"/>
+    <hyperlink ref="O43" r:id="rId27"/>
+    <hyperlink ref="O44" r:id="rId28"/>
+    <hyperlink ref="O45" r:id="rId29"/>
+    <hyperlink ref="O46" r:id="rId30"/>
+    <hyperlink ref="O47" r:id="rId31"/>
+    <hyperlink ref="O49" r:id="rId32"/>
+    <hyperlink ref="O50" r:id="rId33"/>
+    <hyperlink ref="O51" r:id="rId34"/>
+    <hyperlink ref="O12" r:id="rId35"/>
+    <hyperlink ref="O15" r:id="rId36"/>
+    <hyperlink ref="O36" r:id="rId37"/>
+    <hyperlink ref="O26" r:id="rId38"/>
+    <hyperlink ref="O48" r:id="rId39"/>
+    <hyperlink ref="O23" r:id="rId40"/>
+    <hyperlink ref="O52" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId43"/>
-  <drawing r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
+  <drawing r:id="rId43"/>
 </worksheet>
 </file>
--- a/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="305">
   <si>
     <t>Component list</t>
   </si>
@@ -936,6 +936,9 @@
   </si>
   <si>
     <t>Total Cost (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
@@ -1583,6 +1586,38 @@
     <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1614,38 +1649,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2295,15 +2298,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2353,7 +2356,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2378,7 +2381,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2403,7 +2406,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2424,7 +2427,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2445,7 +2448,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2466,7 +2469,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4946,17 +4949,17 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+      <c r="N53" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>96.000900000000016</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -4972,17 +4975,17 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
       <c r="Q54" s="49">
         <f>Q53/5</f>
         <v>19.200180000000003</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5077,15 +5080,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5135,7 +5138,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5160,7 +5163,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5185,7 +5188,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5206,7 +5209,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5227,7 +5230,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5248,7 +5251,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5307,8 +5310,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -5361,10 +5364,10 @@
         <v>2.75</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="76"/>
-    </row>
-    <row r="11" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
+      <c r="S10" s="66"/>
+    </row>
+    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -5419,8 +5422,8 @@
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
+    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -5475,8 +5478,8 @@
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
+    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5531,8 +5534,8 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
+    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -5587,8 +5590,8 @@
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
+    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5643,8 +5646,8 @@
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
+    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -5699,8 +5702,8 @@
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
+    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5755,8 +5758,8 @@
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
     </row>
-    <row r="18" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -5811,8 +5814,8 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
+    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5867,8 +5870,8 @@
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
+    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -5923,8 +5926,8 @@
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
     </row>
-    <row r="21" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5979,64 +5982,64 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="85">
+    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
+      <c r="B22" s="75">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="70" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="80" t="s">
+      <c r="F22" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="80" t="s">
+      <c r="G22" s="70" t="s">
         <v>282</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="70" t="s">
         <v>171</v>
       </c>
       <c r="I22" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="J22" s="80" t="s">
+      <c r="J22" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="K22" s="80" t="s">
-        <v>249</v>
-      </c>
-      <c r="L22" s="80">
+      <c r="K22" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="L22" s="70">
         <v>2</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="70">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N22" s="80">
+      <c r="N22" s="70">
         <v>45</v>
       </c>
-      <c r="O22" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="P22" s="82">
+      <c r="O22" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" s="72">
         <v>0.13789999999999999</v>
       </c>
-      <c r="Q22" s="86">
+      <c r="Q22" s="76">
         <f t="shared" si="7"/>
         <v>6.2054999999999998</v>
       </c>
-      <c r="R22" s="80"/>
-      <c r="S22" s="83"/>
-    </row>
-    <row r="23" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="73"/>
+    </row>
+    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
@@ -6091,8 +6094,8 @@
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
+    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6147,8 +6150,8 @@
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
+    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
@@ -6202,8 +6205,8 @@
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
+    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6258,8 +6261,8 @@
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
+    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
@@ -6314,8 +6317,8 @@
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
+    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6370,8 +6373,8 @@
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
+    <row r="29" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
@@ -6426,8 +6429,8 @@
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="75"/>
+    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6482,8 +6485,8 @@
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75"/>
+    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
@@ -6538,8 +6541,8 @@
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="75"/>
+    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6594,8 +6597,8 @@
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
+    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
@@ -6650,8 +6653,8 @@
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6706,8 +6709,8 @@
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
@@ -6762,8 +6765,8 @@
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
+    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6818,8 +6821,8 @@
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
@@ -6874,8 +6877,8 @@
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6930,8 +6933,8 @@
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
@@ -6986,8 +6989,8 @@
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
@@ -7042,8 +7045,8 @@
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
+    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -7098,8 +7101,8 @@
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
+    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
@@ -7154,8 +7157,8 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+    <row r="43" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -7210,8 +7213,8 @@
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="75"/>
+    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -7266,8 +7269,8 @@
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
     </row>
-    <row r="45" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="75"/>
+    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
@@ -7322,8 +7325,8 @@
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75"/>
+    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -7378,8 +7381,8 @@
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="75"/>
+    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
@@ -7434,8 +7437,8 @@
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
     </row>
-    <row r="48" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
+    <row r="48" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7490,8 +7493,8 @@
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
     </row>
-    <row r="49" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="75"/>
+    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
@@ -7546,8 +7549,8 @@
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
     </row>
-    <row r="50" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A50" s="75"/>
+    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -7602,8 +7605,8 @@
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
-    <row r="51" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
+    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -7658,8 +7661,8 @@
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
     </row>
-    <row r="52" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
+    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -7728,17 +7731,17 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+      <c r="N53" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>291.83290000000005</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -7754,17 +7757,17 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
       <c r="Q54" s="49">
         <f>Q53/20</f>
         <v>14.591645000000003</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7859,15 +7862,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7917,7 +7920,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -7942,7 +7945,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -7967,7 +7970,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -7988,7 +7991,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8009,7 +8012,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8030,7 +8033,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -8145,7 +8148,7 @@
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
     </row>
-    <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
@@ -8761,63 +8764,63 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="85">
+    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
+      <c r="B22" s="75">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="70" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="80" t="s">
+      <c r="F22" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="80" t="s">
+      <c r="G22" s="70" t="s">
         <v>282</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="70" t="s">
         <v>171</v>
       </c>
       <c r="I22" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="J22" s="80" t="s">
+      <c r="J22" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="K22" s="80" t="s">
-        <v>249</v>
-      </c>
-      <c r="L22" s="80">
+      <c r="K22" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="L22" s="70">
         <v>2</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="70">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N22" s="80">
+      <c r="N22" s="70">
         <v>105</v>
       </c>
-      <c r="O22" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="P22" s="82">
+      <c r="O22" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" s="72">
         <v>0.1108</v>
       </c>
-      <c r="Q22" s="82">
+      <c r="Q22" s="72">
         <f t="shared" si="7"/>
         <v>11.634</v>
       </c>
-      <c r="R22" s="80"/>
-      <c r="S22" s="83"/>
-    </row>
-    <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="R22" s="70"/>
+      <c r="S22" s="73"/>
+    </row>
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -9096,7 +9099,7 @@
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -9936,8 +9939,8 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -10104,7 +10107,7 @@
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -10160,7 +10163,7 @@
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -10510,17 +10513,17 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+      <c r="N53" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>633.49189999999999</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -10536,17 +10539,17 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
       <c r="Q54" s="49">
         <f>Q53/50</f>
         <v>12.669838</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10641,15 +10644,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -10699,7 +10702,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -10724,7 +10727,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -10749,7 +10752,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -10770,7 +10773,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -10791,7 +10794,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -10812,7 +10815,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -10871,8 +10874,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -10925,10 +10928,10 @@
         <v>9.4499999999999993</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="76"/>
-    </row>
-    <row r="11" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
+      <c r="S10" s="66"/>
+    </row>
+    <row r="11" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -10983,8 +10986,8 @@
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
+    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -11039,8 +11042,8 @@
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
+    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11095,8 +11098,8 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
+    <row r="14" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -11151,8 +11154,8 @@
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
+    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -11207,8 +11210,8 @@
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
+    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -11263,8 +11266,8 @@
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
+    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -11319,8 +11322,8 @@
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
     </row>
-    <row r="18" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -11375,8 +11378,8 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
+    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -11431,8 +11434,8 @@
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
+    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -11487,8 +11490,8 @@
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
     </row>
-    <row r="21" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11543,62 +11546,62 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="85">
+    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
+      <c r="B22" s="75">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="70" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="80" t="s">
+      <c r="F22" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="80" t="s">
+      <c r="G22" s="70" t="s">
         <v>282</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="70" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="80" t="s">
-        <v>249</v>
-      </c>
-      <c r="J22" s="80" t="s">
+      <c r="I22" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="J22" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80">
+      <c r="K22" s="70"/>
+      <c r="L22" s="70">
         <v>2</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="70">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="N22" s="80">
+      <c r="N22" s="70">
         <v>205</v>
       </c>
-      <c r="O22" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="P22" s="82">
+      <c r="O22" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" s="72">
         <v>0.1108</v>
       </c>
-      <c r="Q22" s="82">
+      <c r="Q22" s="72">
         <f t="shared" si="7"/>
         <v>22.713999999999999</v>
       </c>
-      <c r="R22" s="80"/>
-      <c r="S22" s="83"/>
-    </row>
-    <row r="23" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="73"/>
+    </row>
+    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
@@ -11653,8 +11656,8 @@
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
+    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11709,8 +11712,8 @@
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
+    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
@@ -11764,8 +11767,8 @@
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
+    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11820,8 +11823,8 @@
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
+    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
@@ -11876,8 +11879,8 @@
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" s="77" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
+    <row r="28" spans="1:19" s="67" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -11932,8 +11935,8 @@
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
+    <row r="29" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
@@ -11988,8 +11991,8 @@
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="75"/>
+    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -12044,8 +12047,8 @@
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75"/>
+    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
@@ -12100,8 +12103,8 @@
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="75"/>
+    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -12156,8 +12159,8 @@
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
+    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
@@ -12212,8 +12215,8 @@
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -12268,8 +12271,8 @@
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
@@ -12324,8 +12327,8 @@
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
+    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -12380,8 +12383,8 @@
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
@@ -12436,8 +12439,8 @@
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -12492,8 +12495,8 @@
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
@@ -12548,8 +12551,8 @@
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
@@ -12604,8 +12607,8 @@
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
+    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -12660,8 +12663,8 @@
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
+    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
@@ -12716,8 +12719,8 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+    <row r="43" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -12772,8 +12775,8 @@
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="75"/>
+    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -12828,8 +12831,8 @@
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
     </row>
-    <row r="45" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="75"/>
+    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
@@ -12884,8 +12887,8 @@
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A46" s="75"/>
+    <row r="46" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -12940,8 +12943,8 @@
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="75"/>
+    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
@@ -12996,8 +12999,8 @@
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
     </row>
-    <row r="48" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
+    <row r="48" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -13052,8 +13055,8 @@
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
     </row>
-    <row r="49" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="75"/>
+    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
@@ -13108,8 +13111,8 @@
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
     </row>
-    <row r="50" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A50" s="75"/>
+    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -13164,8 +13167,8 @@
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
-    <row r="51" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
+    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -13220,8 +13223,8 @@
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
     </row>
-    <row r="52" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
+    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -13290,17 +13293,17 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+      <c r="N53" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>1157.7887000000001</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -13316,17 +13319,17 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
       <c r="Q54" s="49">
         <f>Q53/100</f>
         <v>11.577887</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13421,15 +13424,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -13479,7 +13482,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -13504,7 +13507,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -13529,7 +13532,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -13550,7 +13553,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -13571,7 +13574,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -13592,7 +13595,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -13651,8 +13654,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -13705,10 +13708,10 @@
         <v>39.39</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="76"/>
-    </row>
-    <row r="11" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
+      <c r="S10" s="66"/>
+    </row>
+    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -13763,8 +13766,8 @@
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
+    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -13819,8 +13822,8 @@
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
+    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -13875,8 +13878,8 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
+    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -13931,8 +13934,8 @@
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
+    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -13987,8 +13990,8 @@
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
+    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -14043,8 +14046,8 @@
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
+    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14099,8 +14102,8 @@
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
     </row>
-    <row r="18" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -14155,8 +14158,8 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
+    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -14211,8 +14214,8 @@
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
+    <row r="20" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -14267,8 +14270,8 @@
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
     </row>
-    <row r="21" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -14323,8 +14326,8 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="75"/>
+    <row r="22" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="65"/>
       <c r="B22" s="47">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -14347,7 +14350,7 @@
       <c r="H22" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="80" t="s">
+      <c r="I22" s="70" t="s">
         <v>249</v>
       </c>
       <c r="J22" s="37" t="s">
@@ -14364,10 +14367,10 @@
       <c r="N22" s="37">
         <v>1005</v>
       </c>
-      <c r="O22" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="P22" s="82">
+      <c r="O22" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" s="72">
         <v>8.4699999999999998E-2</v>
       </c>
       <c r="Q22" s="38">
@@ -14377,8 +14380,8 @@
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
+    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
@@ -14433,8 +14436,8 @@
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
+    <row r="24" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -14489,8 +14492,8 @@
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
+    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
@@ -14544,8 +14547,8 @@
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
+    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -14600,8 +14603,8 @@
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
+    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
@@ -14656,8 +14659,8 @@
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
+    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -14712,8 +14715,8 @@
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
+    <row r="29" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
@@ -14768,8 +14771,8 @@
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="75"/>
+    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -14824,8 +14827,8 @@
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75"/>
+    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
@@ -14880,8 +14883,8 @@
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="75"/>
+    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -14904,7 +14907,7 @@
       <c r="H32" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="80" t="s">
+      <c r="I32" s="70" t="s">
         <v>249</v>
       </c>
       <c r="J32" s="51" t="s">
@@ -14936,8 +14939,8 @@
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
+    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
@@ -14992,8 +14995,8 @@
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -15048,8 +15051,8 @@
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
@@ -15104,8 +15107,8 @@
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
+    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -15160,8 +15163,8 @@
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
@@ -15216,8 +15219,8 @@
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -15272,8 +15275,8 @@
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
@@ -15328,8 +15331,8 @@
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
@@ -15384,8 +15387,8 @@
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
+    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -15440,8 +15443,8 @@
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
+    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
@@ -15496,8 +15499,8 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -15552,8 +15555,8 @@
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="75"/>
+    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -15608,8 +15611,8 @@
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
     </row>
-    <row r="45" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="75"/>
+    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
@@ -15664,8 +15667,8 @@
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75"/>
+    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -15720,8 +15723,8 @@
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="75"/>
+    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
@@ -15776,8 +15779,8 @@
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
     </row>
-    <row r="48" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
+    <row r="48" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15832,8 +15835,8 @@
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
     </row>
-    <row r="49" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="75"/>
+    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
@@ -15888,8 +15891,8 @@
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
     </row>
-    <row r="50" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A50" s="75"/>
+    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -15944,8 +15947,8 @@
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
-    <row r="51" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
+    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -16000,8 +16003,8 @@
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
     </row>
-    <row r="52" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
+    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -16070,17 +16073,17 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+      <c r="N53" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>5228.3051000000005</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -16096,17 +16099,17 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
       <c r="Q54" s="49">
         <f>Q53/500</f>
         <v>10.456610200000002</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R54" s="83"/>
+      <c r="S54" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16167,7 +16170,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -16201,15 +16204,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -16259,7 +16262,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -16284,7 +16287,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -16309,7 +16312,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -16330,7 +16333,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -16351,7 +16354,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -16372,7 +16375,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -16431,8 +16434,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -16485,12 +16488,12 @@
         <v>59.295000000000002</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="76"/>
-    </row>
-    <row r="11" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
+      <c r="S10" s="66"/>
+    </row>
+    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -16543,8 +16546,8 @@
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
+    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -16599,8 +16602,8 @@
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
+    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16655,8 +16658,8 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
+    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -16711,8 +16714,8 @@
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
+    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -16767,8 +16770,8 @@
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
+    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -16823,8 +16826,8 @@
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
+    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -16879,8 +16882,8 @@
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
     </row>
-    <row r="18" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -16935,8 +16938,8 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
+    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -16991,8 +16994,8 @@
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
+    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -17047,8 +17050,8 @@
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
     </row>
-    <row r="21" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -17103,62 +17106,62 @@
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="85">
+    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
+      <c r="B22" s="75">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="70" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="80" t="s">
+      <c r="F22" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="80" t="s">
+      <c r="G22" s="70" t="s">
         <v>282</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="70" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="80" t="s">
-        <v>249</v>
-      </c>
-      <c r="J22" s="80" t="s">
+      <c r="I22" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="J22" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80">
+      <c r="K22" s="70"/>
+      <c r="L22" s="70">
         <v>2</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="70">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="N22" s="80">
+      <c r="N22" s="70">
         <v>2005</v>
       </c>
-      <c r="O22" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="P22" s="82">
+      <c r="O22" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" s="72">
         <v>8.4699999999999998E-2</v>
       </c>
-      <c r="Q22" s="82">
+      <c r="Q22" s="72">
         <f t="shared" si="7"/>
         <v>169.8235</v>
       </c>
-      <c r="R22" s="80"/>
-      <c r="S22" s="83"/>
-    </row>
-    <row r="23" spans="1:19" s="77" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="73"/>
+    </row>
+    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
@@ -17213,8 +17216,8 @@
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
+    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -17269,8 +17272,8 @@
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
+    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
@@ -17324,8 +17327,8 @@
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" s="77" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
+    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -17380,8 +17383,8 @@
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
+    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
@@ -17436,8 +17439,8 @@
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
+    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -17492,8 +17495,8 @@
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
+    <row r="29" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
@@ -17548,8 +17551,8 @@
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" s="77" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="75"/>
+    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -17604,8 +17607,8 @@
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75"/>
+    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
@@ -17660,8 +17663,8 @@
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="75"/>
+    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -17684,7 +17687,7 @@
       <c r="H32" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="80" t="s">
+      <c r="I32" s="70" t="s">
         <v>249</v>
       </c>
       <c r="J32" s="51" t="s">
@@ -17716,8 +17719,8 @@
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
+    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
@@ -17772,8 +17775,8 @@
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -17828,8 +17831,8 @@
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
@@ -17884,8 +17887,8 @@
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
+    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -17940,8 +17943,8 @@
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
@@ -17996,8 +17999,8 @@
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -18052,8 +18055,8 @@
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
@@ -18108,8 +18111,8 @@
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
@@ -18164,8 +18167,8 @@
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
+    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -18220,8 +18223,8 @@
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
+    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
@@ -18276,8 +18279,8 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -18332,8 +18335,8 @@
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="75"/>
+    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -18388,8 +18391,8 @@
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
     </row>
-    <row r="45" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="75"/>
+    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
@@ -18444,8 +18447,8 @@
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75"/>
+    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -18500,8 +18503,8 @@
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="75"/>
+    <row r="47" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
@@ -18556,8 +18559,8 @@
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
     </row>
-    <row r="48" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
+    <row r="48" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -18612,8 +18615,8 @@
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
     </row>
-    <row r="49" spans="1:19" s="77" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="75"/>
+    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
@@ -18668,8 +18671,8 @@
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
     </row>
-    <row r="50" spans="1:19" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="75"/>
+    <row r="50" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -18724,8 +18727,8 @@
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
-    <row r="51" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
+    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -18780,8 +18783,8 @@
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
     </row>
-    <row r="52" spans="1:19" s="77" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
+    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -18836,65 +18839,115 @@
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
     </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="73" t="s">
+    <row r="53" spans="1:19" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51"/>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f t="shared" ref="M53" si="21">L53*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="N53" s="51">
+        <v>1000</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" ref="Q53" si="22">P53*N53</f>
+        <v>4070.0000000000005</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
+    </row>
+    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O53" s="74"/>
-      <c r="P53" s="74"/>
-      <c r="Q53" s="48">
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
+      <c r="Q54" s="48">
         <f>SUM(Q10:Q52)</f>
         <v>9944.2944000000043</v>
       </c>
-      <c r="R53" s="69"/>
-      <c r="S53" s="70"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="73" t="s">
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="74"/>
-      <c r="P54" s="74"/>
-      <c r="Q54" s="49">
-        <f>Q53/1000</f>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/1000</f>
         <v>9.944294400000004</v>
       </c>
-      <c r="R54" s="71"/>
-      <c r="S54" s="72"/>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R54:S55"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -18939,8 +18992,9 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
--- a/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSpark_BOM_EthPoE-Module-v2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="307">
   <si>
     <t>Component list</t>
   </si>
@@ -939,6 +939,12 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>POE Injector</t>
+  </si>
+  <si>
+    <t>HKBTM</t>
   </si>
 </sst>
 </file>
@@ -2262,7 +2268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2283,8 +2289,7 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2587,7 +2592,7 @@
     <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -4860,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="51">
-        <f t="shared" ref="M51:M52" si="41">L51*5</f>
+        <f t="shared" ref="M51:M53" si="41">L51*5</f>
         <v>5</v>
       </c>
       <c r="N51" s="51">
@@ -4873,7 +4878,7 @@
         <v>0.25240000000000001</v>
       </c>
       <c r="Q51" s="52">
-        <f t="shared" ref="Q51:Q52" si="42">P51*N51</f>
+        <f t="shared" ref="Q51:Q53" si="42">P51*N51</f>
         <v>1.5144000000000002</v>
       </c>
       <c r="R51" s="51"/>
@@ -4935,65 +4940,121 @@
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
     </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="85" t="s">
+    <row r="53" spans="1:19" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="51">
+        <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>96.000900000000016</v>
-      </c>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
+      <c r="N53" s="51">
+        <v>1</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" si="42"/>
+        <v>4.07</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
     </row>
     <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
       <c r="N54" s="85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
-      <c r="Q54" s="49">
-        <f>Q53/5</f>
-        <v>19.200180000000003</v>
-      </c>
-      <c r="R54" s="83"/>
-      <c r="S54" s="84"/>
+      <c r="Q54" s="48">
+        <f>SUM(Q10:Q53)</f>
+        <v>100.07090000000002</v>
+      </c>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/5</f>
+        <v>20.014180000000003</v>
+      </c>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R53:S54"/>
-    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R54:S55"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -5038,16 +5099,17 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId43"/>
-  <drawing r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId44"/>
+  <drawing r:id="rId45"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -5067,9 +5129,11 @@
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.42578125" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -5090,7 +5154,7 @@
       <c r="R1" s="77"/>
       <c r="S1" s="78"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -5115,7 +5179,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -5140,7 +5204,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="79"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -5165,7 +5229,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="80"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -5190,7 +5254,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="80"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -5211,7 +5275,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="80"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -5232,7 +5296,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="80"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -5253,7 +5317,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="80"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -5310,7 +5374,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -5365,11 +5429,15 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="65"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -5403,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M52" si="1">L11*20</f>
+        <f t="shared" ref="M11:M53" si="1">L11*20</f>
         <v>20</v>
       </c>
       <c r="N11" s="51">
@@ -5421,8 +5489,12 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -5477,8 +5549,12 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -5533,8 +5609,12 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+    </row>
+    <row r="14" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -5589,8 +5669,12 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -5645,8 +5729,12 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+    </row>
+    <row r="16" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -5701,8 +5789,12 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -5757,8 +5849,12 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -5813,8 +5909,12 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -5869,8 +5969,12 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+    </row>
+    <row r="20" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -5925,8 +6029,12 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -5981,8 +6089,12 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
       <c r="B22" s="75">
         <f t="shared" si="0"/>
@@ -6037,8 +6149,12 @@
       </c>
       <c r="R22" s="70"/>
       <c r="S22" s="73"/>
-    </row>
-    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -6093,8 +6209,12 @@
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
@@ -6149,8 +6269,12 @@
       </c>
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -6204,8 +6328,12 @@
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
@@ -6260,8 +6388,12 @@
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -6316,8 +6448,12 @@
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -6372,8 +6508,12 @@
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -6428,8 +6568,12 @@
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
@@ -6484,8 +6628,12 @@
       </c>
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -6540,8 +6688,12 @@
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
@@ -6596,8 +6748,12 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -6652,8 +6808,12 @@
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
@@ -6708,8 +6868,12 @@
       </c>
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -6764,8 +6928,12 @@
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -6820,8 +6988,12 @@
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -6876,8 +7048,12 @@
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+    </row>
+    <row r="38" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
@@ -6932,8 +7108,12 @@
       </c>
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+    </row>
+    <row r="39" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -6988,8 +7168,12 @@
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+    </row>
+    <row r="40" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -7044,8 +7228,12 @@
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+    </row>
+    <row r="41" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
@@ -7100,8 +7288,12 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+    </row>
+    <row r="42" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -7156,8 +7348,12 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+    </row>
+    <row r="43" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -7212,8 +7408,12 @@
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+    </row>
+    <row r="44" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
@@ -7268,8 +7468,12 @@
       </c>
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+    </row>
+    <row r="45" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -7324,8 +7528,12 @@
       </c>
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+    </row>
+    <row r="46" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -7380,8 +7588,12 @@
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+    </row>
+    <row r="47" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -7436,8 +7648,12 @@
       </c>
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+    </row>
+    <row r="48" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
@@ -7492,8 +7708,12 @@
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+    </row>
+    <row r="49" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -7548,8 +7768,12 @@
       </c>
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+    </row>
+    <row r="50" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
@@ -7599,13 +7823,17 @@
         <v>2.3896000000000002</v>
       </c>
       <c r="Q50" s="52">
-        <f t="shared" ref="Q50:Q52" si="20">P50*N50</f>
+        <f t="shared" ref="Q50:Q53" si="20">P50*N50</f>
         <v>50.181600000000003</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U50"/>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+    </row>
+    <row r="51" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
@@ -7660,8 +7888,12 @@
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
-    </row>
-    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+    </row>
+    <row r="52" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
@@ -7716,66 +7948,126 @@
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
-    </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="85" t="s">
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+    </row>
+    <row r="53" spans="1:24" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N53" s="51">
+        <v>1</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" si="20"/>
+        <v>4.07</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="85" t="s">
         <v>5</v>
-      </c>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>291.83290000000005</v>
-      </c>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="85" t="s">
-        <v>6</v>
       </c>
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
-      <c r="Q54" s="49">
-        <f>Q53/20</f>
-        <v>14.591645000000003</v>
-      </c>
-      <c r="R54" s="83"/>
-      <c r="S54" s="84"/>
+      <c r="Q54" s="48">
+        <f>SUM(Q10:Q53)</f>
+        <v>295.90290000000005</v>
+      </c>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/20</f>
+        <v>14.795145000000002</v>
+      </c>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R54:S55"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -7820,15 +8112,16 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -7849,9 +8142,12 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.140625" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -7872,7 +8168,7 @@
       <c r="R1" s="77"/>
       <c r="S1" s="78"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -7897,7 +8193,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -7922,7 +8218,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="79"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -7947,7 +8243,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="80"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -7972,7 +8268,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="80"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -7993,7 +8289,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="80"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -8014,7 +8310,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="80"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -8034,8 +8330,13 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="80"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -8091,8 +8392,13 @@
       <c r="S9" s="30" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+    </row>
+    <row r="10" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -8147,11 +8453,16 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
-    </row>
-    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+    </row>
+    <row r="11" spans="1:25" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -8185,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M52" si="1">L11*50</f>
+        <f t="shared" ref="M11:M53" si="1">L11*50</f>
         <v>50</v>
       </c>
       <c r="N11" s="51">
@@ -8203,8 +8514,13 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -8259,8 +8575,13 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
+      <c r="Y12" s="67"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -8315,8 +8636,13 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U13" s="67"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -8371,8 +8697,13 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U14" s="67"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -8427,8 +8758,13 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -8483,8 +8819,13 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -8539,8 +8880,13 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -8595,8 +8941,13 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -8651,8 +9002,13 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+    </row>
+    <row r="20" spans="1:25" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -8707,8 +9063,13 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -8763,8 +9124,13 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+    </row>
+    <row r="22" spans="1:25" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
       <c r="B22" s="75">
         <f t="shared" si="0"/>
@@ -8819,8 +9185,13 @@
       </c>
       <c r="R22" s="70"/>
       <c r="S22" s="73"/>
-    </row>
-    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+    </row>
+    <row r="23" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -8875,8 +9246,13 @@
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
@@ -8931,8 +9307,13 @@
       </c>
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+    </row>
+    <row r="25" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -8986,8 +9367,13 @@
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+    </row>
+    <row r="26" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
@@ -9042,8 +9428,13 @@
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+    </row>
+    <row r="27" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -9098,8 +9489,13 @@
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67"/>
+    </row>
+    <row r="28" spans="1:25" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -9154,8 +9550,13 @@
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+    </row>
+    <row r="29" spans="1:25" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -9210,8 +9611,13 @@
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+    </row>
+    <row r="30" spans="1:25" ht="36" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
@@ -9266,8 +9672,13 @@
       </c>
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -9322,8 +9733,13 @@
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
@@ -9378,8 +9794,13 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U32" s="67"/>
+      <c r="V32" s="67"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="67"/>
+      <c r="Y32" s="67"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -9434,8 +9855,13 @@
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U33" s="67"/>
+      <c r="V33" s="67"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="67"/>
+      <c r="Y33" s="67"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
@@ -9490,8 +9916,13 @@
       </c>
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U34" s="67"/>
+      <c r="V34" s="67"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+    </row>
+    <row r="35" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -9546,8 +9977,13 @@
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U35" s="67"/>
+      <c r="V35" s="67"/>
+      <c r="W35" s="67"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="67"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -9602,8 +10038,13 @@
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U36" s="67"/>
+      <c r="V36" s="67"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -9658,8 +10099,13 @@
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U37" s="67"/>
+      <c r="V37" s="67"/>
+      <c r="W37" s="67"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
@@ -9714,8 +10160,13 @@
       </c>
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U38" s="67"/>
+      <c r="V38" s="67"/>
+      <c r="W38" s="67"/>
+      <c r="X38" s="67"/>
+      <c r="Y38" s="67"/>
+    </row>
+    <row r="39" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -9770,8 +10221,13 @@
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U39" s="67"/>
+      <c r="V39" s="67"/>
+      <c r="W39" s="67"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="67"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -9826,8 +10282,13 @@
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U40" s="67"/>
+      <c r="V40" s="67"/>
+      <c r="W40" s="67"/>
+      <c r="X40" s="67"/>
+      <c r="Y40" s="67"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
@@ -9882,8 +10343,13 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U41" s="67"/>
+      <c r="V41" s="67"/>
+      <c r="W41" s="67"/>
+      <c r="X41" s="67"/>
+      <c r="Y41" s="67"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -9938,8 +10404,13 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+      <c r="X42" s="67"/>
+      <c r="Y42" s="67"/>
+    </row>
+    <row r="43" spans="1:25" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -9995,7 +10466,7 @@
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
@@ -10050,8 +10521,13 @@
       </c>
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U44" s="67"/>
+      <c r="V44" s="67"/>
+      <c r="W44" s="67"/>
+      <c r="X44" s="67"/>
+      <c r="Y44" s="67"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -10106,8 +10582,13 @@
       </c>
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U45" s="67"/>
+      <c r="V45" s="67"/>
+      <c r="W45" s="67"/>
+      <c r="X45" s="67"/>
+      <c r="Y45" s="67"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -10162,8 +10643,13 @@
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U46" s="67"/>
+      <c r="V46" s="67"/>
+      <c r="W46" s="67"/>
+      <c r="X46" s="67"/>
+      <c r="Y46" s="67"/>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -10218,8 +10704,13 @@
       </c>
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U47" s="67"/>
+      <c r="V47" s="67"/>
+      <c r="W47" s="67"/>
+      <c r="X47" s="67"/>
+      <c r="Y47" s="67"/>
+    </row>
+    <row r="48" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
@@ -10274,8 +10765,13 @@
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="U48" s="67"/>
+      <c r="V48" s="67"/>
+      <c r="W48" s="67"/>
+      <c r="X48" s="67"/>
+      <c r="Y48" s="67"/>
+    </row>
+    <row r="49" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -10330,8 +10826,13 @@
       </c>
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U49" s="67"/>
+      <c r="V49" s="67"/>
+      <c r="W49" s="67"/>
+      <c r="X49" s="67"/>
+      <c r="Y49" s="67"/>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
@@ -10381,13 +10882,18 @@
         <v>2.2336999999999998</v>
       </c>
       <c r="Q50" s="52">
-        <f t="shared" ref="Q50:Q52" si="20">P50*N50</f>
+        <f t="shared" ref="Q50:Q53" si="20">P50*N50</f>
         <v>113.91869999999999</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U50" s="67"/>
+      <c r="V50" s="67"/>
+      <c r="W50" s="67"/>
+      <c r="X50" s="67"/>
+      <c r="Y50" s="67"/>
+    </row>
+    <row r="51" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
@@ -10442,8 +10948,13 @@
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U51" s="67"/>
+      <c r="V51" s="67"/>
+      <c r="W51" s="67"/>
+      <c r="X51" s="67"/>
+      <c r="Y51" s="67"/>
+    </row>
+    <row r="52" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
@@ -10498,66 +11009,127 @@
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
-    </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="85" t="s">
+      <c r="U52" s="67"/>
+      <c r="V52" s="67"/>
+      <c r="W52" s="67"/>
+      <c r="X52" s="67"/>
+      <c r="Y52" s="67"/>
+    </row>
+    <row r="53" spans="1:25" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N53" s="51">
+        <v>1</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" si="20"/>
+        <v>4.07</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
+    </row>
+    <row r="54" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="85" t="s">
         <v>5</v>
-      </c>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>633.49189999999999</v>
-      </c>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="85" t="s">
-        <v>6</v>
       </c>
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
-      <c r="Q54" s="49">
-        <f>Q53/50</f>
-        <v>12.669838</v>
-      </c>
-      <c r="R54" s="83"/>
-      <c r="S54" s="84"/>
+      <c r="Q54" s="48">
+        <f>SUM(Q10:Q53)</f>
+        <v>637.56190000000004</v>
+      </c>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/50</f>
+        <v>12.751238000000001</v>
+      </c>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R54:S55"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -10602,15 +11174,16 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -10631,9 +11204,11 @@
     <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -10654,7 +11229,7 @@
       <c r="R1" s="77"/>
       <c r="S1" s="78"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -10679,7 +11254,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -10704,7 +11279,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="79"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -10729,7 +11304,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="80"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -10754,7 +11329,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="80"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -10775,7 +11350,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="80"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -10796,7 +11371,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="80"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -10817,7 +11392,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="80"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -10874,7 +11449,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -10929,11 +11504,15 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A11" s="65"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -10967,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M52" si="1">L11*100</f>
+        <f t="shared" ref="M11:M53" si="1">L11*100</f>
         <v>100</v>
       </c>
       <c r="N11" s="51">
@@ -10985,8 +11564,12 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -11041,8 +11624,12 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -11097,8 +11684,12 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+    </row>
+    <row r="14" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -11153,8 +11744,12 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -11209,8 +11804,12 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+    </row>
+    <row r="16" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -11265,8 +11864,12 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -11321,8 +11924,12 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -11377,8 +11984,12 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -11433,8 +12044,12 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+    </row>
+    <row r="20" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -11489,8 +12104,12 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -11545,8 +12164,12 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
       <c r="B22" s="75">
         <f t="shared" si="0"/>
@@ -11599,8 +12222,12 @@
       </c>
       <c r="R22" s="70"/>
       <c r="S22" s="73"/>
-    </row>
-    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -11655,8 +12282,12 @@
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
@@ -11711,8 +12342,12 @@
       </c>
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -11766,8 +12401,12 @@
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
@@ -11822,8 +12461,12 @@
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -11878,8 +12521,12 @@
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" s="67" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="1:24" s="67" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -11934,8 +12581,12 @@
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -11990,8 +12641,12 @@
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
@@ -12046,8 +12701,12 @@
       </c>
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -12102,8 +12761,12 @@
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
@@ -12158,8 +12821,12 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -12214,8 +12881,12 @@
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
@@ -12270,8 +12941,12 @@
       </c>
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -12326,8 +13001,12 @@
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -12382,8 +13061,12 @@
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -12438,8 +13121,12 @@
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+    </row>
+    <row r="38" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
@@ -12494,8 +13181,12 @@
       </c>
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+    </row>
+    <row r="39" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -12550,8 +13241,12 @@
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+    </row>
+    <row r="40" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -12606,8 +13301,12 @@
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+    </row>
+    <row r="41" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
@@ -12662,8 +13361,12 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+    </row>
+    <row r="42" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -12718,8 +13421,12 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+    </row>
+    <row r="43" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -12774,8 +13481,12 @@
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+    </row>
+    <row r="44" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
@@ -12830,8 +13541,12 @@
       </c>
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+    </row>
+    <row r="45" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -12886,8 +13601,12 @@
       </c>
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+    </row>
+    <row r="46" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -12942,8 +13661,12 @@
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+    </row>
+    <row r="47" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -12998,8 +13721,12 @@
       </c>
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+    </row>
+    <row r="48" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
@@ -13054,8 +13781,12 @@
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+    </row>
+    <row r="49" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -13110,8 +13841,12 @@
       </c>
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+    </row>
+    <row r="50" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
@@ -13161,13 +13896,17 @@
         <v>2.0236999999999998</v>
       </c>
       <c r="Q50" s="52">
-        <f t="shared" ref="Q50:Q52" si="20">P50*N50</f>
+        <f t="shared" ref="Q50:Q53" si="20">P50*N50</f>
         <v>204.3937</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U50"/>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+    </row>
+    <row r="51" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
@@ -13222,8 +13961,12 @@
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
-    </row>
-    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+    </row>
+    <row r="52" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
@@ -13278,66 +14021,126 @@
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
-    </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="85" t="s">
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+    </row>
+    <row r="53" spans="1:24" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N53" s="51">
+        <v>1</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" si="20"/>
+        <v>4.07</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="85" t="s">
         <v>5</v>
-      </c>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>1157.7887000000001</v>
-      </c>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="85" t="s">
-        <v>6</v>
       </c>
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
-      <c r="Q54" s="49">
-        <f>Q53/100</f>
-        <v>11.577887</v>
-      </c>
-      <c r="R54" s="83"/>
-      <c r="S54" s="84"/>
+      <c r="Q54" s="48">
+        <f>SUM(Q10:Q53)</f>
+        <v>1161.8587</v>
+      </c>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/100</f>
+        <v>11.618587</v>
+      </c>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R54:S55"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -13382,15 +14185,16 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -13411,9 +14215,11 @@
     <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.42578125" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -13434,7 +14240,7 @@
       <c r="R1" s="77"/>
       <c r="S1" s="78"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -13459,7 +14265,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -13484,7 +14290,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="79"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -13509,7 +14315,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="80"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -13534,7 +14340,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="80"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -13555,7 +14361,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="80"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -13576,7 +14382,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="80"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -13597,7 +14403,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="80"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -13654,7 +14460,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -13709,11 +14515,15 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="65"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B52" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -13747,7 +14557,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M52" si="1">L11*500</f>
+        <f t="shared" ref="M11:M53" si="1">L11*500</f>
         <v>500</v>
       </c>
       <c r="N11" s="51">
@@ -13765,8 +14575,12 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -13821,8 +14635,12 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -13877,8 +14695,12 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+    </row>
+    <row r="14" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -13933,8 +14755,12 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -13989,8 +14815,12 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+    </row>
+    <row r="16" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -14045,8 +14875,12 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -14101,8 +14935,12 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -14157,8 +14995,12 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -14213,8 +15055,12 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+    </row>
+    <row r="20" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -14269,8 +15115,12 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -14325,8 +15175,12 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65"/>
       <c r="B22" s="47">
         <f t="shared" si="0"/>
@@ -14379,8 +15233,12 @@
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
-    </row>
-    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -14435,8 +15293,12 @@
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
@@ -14491,8 +15353,12 @@
       </c>
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -14546,8 +15412,12 @@
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
@@ -14602,8 +15472,12 @@
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -14658,8 +15532,12 @@
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -14714,8 +15592,12 @@
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -14770,8 +15652,12 @@
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
@@ -14826,8 +15712,12 @@
       </c>
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -14882,8 +15772,12 @@
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
@@ -14938,8 +15832,12 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -14994,8 +15892,12 @@
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
@@ -15050,8 +15952,12 @@
       </c>
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -15106,8 +16012,12 @@
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -15162,8 +16072,12 @@
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -15218,8 +16132,12 @@
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+    </row>
+    <row r="38" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
@@ -15274,8 +16192,12 @@
       </c>
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+    </row>
+    <row r="39" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -15330,8 +16252,12 @@
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+    </row>
+    <row r="40" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -15386,8 +16312,12 @@
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+    </row>
+    <row r="41" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
@@ -15442,8 +16372,12 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+    </row>
+    <row r="42" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -15498,8 +16432,12 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+    </row>
+    <row r="43" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -15554,8 +16492,12 @@
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+    </row>
+    <row r="44" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
@@ -15610,8 +16552,12 @@
       </c>
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+    </row>
+    <row r="45" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -15666,8 +16612,12 @@
       </c>
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+    </row>
+    <row r="46" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -15722,8 +16672,12 @@
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+    </row>
+    <row r="47" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -15778,8 +16732,12 @@
       </c>
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+    </row>
+    <row r="48" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
@@ -15834,8 +16792,12 @@
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+    </row>
+    <row r="49" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -15890,8 +16852,12 @@
       </c>
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+    </row>
+    <row r="50" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
@@ -15941,13 +16907,17 @@
         <v>1.9489000000000001</v>
       </c>
       <c r="Q50" s="52">
-        <f t="shared" ref="Q50:Q52" si="20">P50*N50</f>
+        <f t="shared" ref="Q50:Q53" si="20">P50*N50</f>
         <v>976.39890000000003</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U50"/>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+    </row>
+    <row r="51" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
@@ -16002,8 +16972,12 @@
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
-    </row>
-    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+    </row>
+    <row r="52" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
@@ -16058,66 +17032,126 @@
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
-    </row>
-    <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="85" t="s">
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+    </row>
+    <row r="53" spans="1:24" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="47">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="51">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N53" s="51">
+        <v>1</v>
+      </c>
+      <c r="O53" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" s="52">
+        <v>4.07</v>
+      </c>
+      <c r="Q53" s="52">
+        <f t="shared" si="20"/>
+        <v>4.07</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="39"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="85" t="s">
         <v>5</v>
-      </c>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>5228.3051000000005</v>
-      </c>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="85" t="s">
-        <v>6</v>
       </c>
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
-      <c r="Q54" s="49">
-        <f>Q53/500</f>
-        <v>10.456610200000002</v>
-      </c>
-      <c r="R54" s="83"/>
-      <c r="S54" s="84"/>
+      <c r="Q54" s="48">
+        <f>SUM(Q10:Q53)</f>
+        <v>5232.3751000000002</v>
+      </c>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="86"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="49">
+        <f>Q54/500</f>
+        <v>10.464750200000001</v>
+      </c>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R53:S54"/>
     <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R54:S55"/>
+    <mergeCell ref="N55:P55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -16162,15 +17196,16 @@
     <hyperlink ref="O23" r:id="rId40"/>
     <hyperlink ref="O52" r:id="rId41"/>
     <hyperlink ref="O22" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -16191,9 +17226,11 @@
     <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.140625" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -16214,7 +17251,7 @@
       <c r="R1" s="77"/>
       <c r="S1" s="78"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -16239,7 +17276,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -16264,7 +17301,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="79"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -16289,7 +17326,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="80"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -16314,7 +17351,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="80"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -16335,7 +17372,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="80"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -16356,7 +17393,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="80"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -16377,7 +17414,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="80"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -16434,7 +17471,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="65"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -16489,8 +17526,12 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="65"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
@@ -16545,8 +17586,12 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -16601,8 +17646,12 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="65"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -16657,8 +17706,12 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+    </row>
+    <row r="14" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -16713,8 +17766,12 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="65"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -16769,8 +17826,12 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+    </row>
+    <row r="16" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -16825,8 +17886,12 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="65"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -16881,8 +17946,12 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -16937,8 +18006,12 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="65"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -16993,8 +18066,12 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+    </row>
+    <row r="20" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="65"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -17049,8 +18126,12 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="65"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -17105,8 +18186,12 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
       <c r="B22" s="75">
         <f t="shared" si="0"/>
@@ -17159,8 +18244,12 @@
       </c>
       <c r="R22" s="70"/>
       <c r="S22" s="73"/>
-    </row>
-    <row r="23" spans="1:19" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="1:24" s="67" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="65"/>
       <c r="B23" s="46">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -17215,8 +18304,12 @@
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="65"/>
       <c r="B24" s="47">
         <f t="shared" si="0"/>
@@ -17271,8 +18364,12 @@
       </c>
       <c r="R24" s="51"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="65"/>
       <c r="B25" s="46">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -17326,8 +18423,12 @@
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="1:24" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="65"/>
       <c r="B26" s="47">
         <f t="shared" si="0"/>
@@ -17382,8 +18483,12 @@
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="65"/>
       <c r="B27" s="46">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -17438,8 +18543,12 @@
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="65"/>
       <c r="B28" s="47">
         <f t="shared" si="0"/>
@@ -17494,8 +18603,12 @@
       </c>
       <c r="R28" s="51"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="65"/>
       <c r="B29" s="46">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -17550,8 +18663,12 @@
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="1:24" s="67" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A30" s="65"/>
       <c r="B30" s="47">
         <f t="shared" si="0"/>
@@ -17606,8 +18723,12 @@
       </c>
       <c r="R30" s="51"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="65"/>
       <c r="B31" s="46">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -17662,8 +18783,12 @@
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
@@ -17718,8 +18843,12 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="65"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -17774,8 +18903,12 @@
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65"/>
       <c r="B34" s="47">
         <f t="shared" si="0"/>
@@ -17830,8 +18963,12 @@
       </c>
       <c r="R34" s="51"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="65"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -17886,8 +19023,12 @@
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -17942,8 +19083,12 @@
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="65"/>
       <c r="B37" s="46">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -17998,8 +19143,12 @@
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+    </row>
+    <row r="38" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65"/>
       <c r="B38" s="47">
         <f t="shared" si="0"/>
@@ -18054,8 +19203,12 @@
       </c>
       <c r="R38" s="51"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+    </row>
+    <row r="39" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="65"/>
       <c r="B39" s="46">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -18110,8 +19263,12 @@
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+    </row>
+    <row r="40" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65"/>
       <c r="B40" s="47">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -18166,8 +19323,12 @@
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+    </row>
+    <row r="41" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="65"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
@@ -18222,8 +19383,12 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+    </row>
+    <row r="42" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -18278,8 +19443,12 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+    </row>
+    <row r="43" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="B43" s="46">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -18334,8 +19503,12 @@
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+    </row>
+    <row r="44" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="65"/>
       <c r="B44" s="47">
         <f t="shared" si="0"/>
@@ -18390,8 +19563,12 @@
       </c>
       <c r="R44" s="51"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+    </row>
+    <row r="45" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="65"/>
       <c r="B45" s="46">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -18446,8 +19623,12 @@
       </c>
       <c r="R45" s="37"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+    </row>
+    <row r="46" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="65"/>
       <c r="B46" s="47">
         <f t="shared" si="0"/>
@@ -18502,8 +19683,12 @@
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+    </row>
+    <row r="47" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="65"/>
       <c r="B47" s="46">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -18558,8 +19743,12 @@
       </c>
       <c r="R47" s="37"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+    </row>
+    <row r="48" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="65"/>
       <c r="B48" s="47">
         <f t="shared" si="0"/>
@@ -18614,8 +19803,12 @@
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+    </row>
+    <row r="49" spans="1:24" s="67" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="65"/>
       <c r="B49" s="46">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -18670,8 +19863,12 @@
       </c>
       <c r="R49" s="37"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+    </row>
+    <row r="50" spans="1:24" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="65"/>
       <c r="B50" s="47">
         <f t="shared" si="0"/>
@@ -18726,8 +19923,12 @@
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U50"/>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+    </row>
+    <row r="51" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="65"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
@@ -18782,8 +19983,12 @@
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="39"/>
-    </row>
-    <row r="52" spans="1:19" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+    </row>
+    <row r="52" spans="1:24" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="65"/>
       <c r="B52" s="47">
         <f t="shared" si="0"/>
@@ -18838,8 +20043,12 @@
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="39"/>
-    </row>
-    <row r="53" spans="1:19" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+    </row>
+    <row r="53" spans="1:24" s="67" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="65"/>
       <c r="B53" s="47">
         <f t="shared" si="0"/>
@@ -18857,12 +20066,18 @@
       <c r="F53" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
+      <c r="G53" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" s="51" t="s">
+        <v>306</v>
+      </c>
       <c r="I53" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="J53" s="51"/>
+      <c r="J53" s="51" t="s">
+        <v>249</v>
+      </c>
       <c r="K53" s="51" t="s">
         <v>249</v>
       </c>
@@ -18874,7 +20089,7 @@
         <v>1000</v>
       </c>
       <c r="N53" s="51">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="O53" s="61" t="s">
         <v>304</v>
@@ -18884,12 +20099,16 @@
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="22">P53*N53</f>
-        <v>4070.0000000000005</v>
+        <v>4.07</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="39"/>
-    </row>
-    <row r="54" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U53"/>
+      <c r="V53"/>
+      <c r="W53"/>
+      <c r="X53"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="40"/>
       <c r="C54" s="41"/>
@@ -18909,13 +20128,13 @@
       <c r="O54" s="86"/>
       <c r="P54" s="86"/>
       <c r="Q54" s="48">
-        <f>SUM(Q10:Q52)</f>
-        <v>9944.2944000000043</v>
+        <f>SUM(Q10:Q53)</f>
+        <v>9948.364400000004</v>
       </c>
       <c r="R54" s="81"/>
       <c r="S54" s="82"/>
     </row>
-    <row r="55" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="25"/>
       <c r="C55" s="36"/>
@@ -18936,7 +20155,7 @@
       <c r="P55" s="86"/>
       <c r="Q55" s="49">
         <f>Q54/1000</f>
-        <v>9.944294400000004</v>
+        <v>9.9483644000000044</v>
       </c>
       <c r="R55" s="83"/>
       <c r="S55" s="84"/>
